--- a/data/1/6.3 fig1 p 18.xlsx
+++ b/data/1/6.3 fig1 p 18.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="8955"/>
+    <workbookView windowWidth="27945" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="6.3 fig1 43p 18" sheetId="1" r:id="rId1"/>
@@ -73,16 +73,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -90,7 +90,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -98,14 +98,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -113,7 +113,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -121,7 +121,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -129,7 +129,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -137,7 +137,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -145,14 +145,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -160,7 +160,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -168,7 +168,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -176,14 +176,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -191,42 +191,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -536,19 +536,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -687,55 +687,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1219,7 +1219,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultColWidth="9.55752212389381" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.56190476190476" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="C1" t="s">
@@ -1450,13 +1450,13 @@
         <v>6.8</v>
       </c>
       <c r="L5">
-        <v>8.49</v>
+        <v>8.19</v>
       </c>
       <c r="M5">
-        <v>8.43</v>
+        <v>8.13</v>
       </c>
       <c r="N5">
-        <v>8.52</v>
+        <v>8.12</v>
       </c>
       <c r="O5">
         <v>9.48</v>
@@ -1500,13 +1500,13 @@
         <v>5.82</v>
       </c>
       <c r="L6">
-        <v>8.22</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>8.55</v>
+        <v>8.05</v>
       </c>
       <c r="N6">
-        <v>8.5</v>
+        <v>8.05</v>
       </c>
       <c r="O6">
         <v>9.44</v>
@@ -1738,13 +1738,13 @@
         <v>9.28</v>
       </c>
       <c r="I12">
-        <v>6.09</v>
+        <v>6.19</v>
       </c>
       <c r="J12">
-        <v>6.02</v>
+        <v>6.22</v>
       </c>
       <c r="K12">
-        <v>5.91</v>
+        <v>6.3</v>
       </c>
       <c r="L12">
         <v>8.3</v>
@@ -1791,7 +1791,7 @@
         <v>5.99</v>
       </c>
       <c r="J13">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>5.88</v>
@@ -1917,49 +1917,49 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>7.2</v>
+        <v>8.2</v>
       </c>
       <c r="D17">
-        <v>7.35</v>
+        <v>8.35</v>
       </c>
       <c r="E17">
-        <v>7.3</v>
+        <v>8.3</v>
       </c>
       <c r="F17">
-        <v>6.74</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>6.8</v>
+        <v>7.22</v>
       </c>
       <c r="H17">
-        <v>6.78</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>6.23</v>
+        <v>6.53</v>
       </c>
       <c r="J17">
-        <v>6.27</v>
+        <v>6.67</v>
       </c>
       <c r="K17">
         <v>6.44</v>
       </c>
       <c r="L17">
-        <v>7.16</v>
+        <v>8.16</v>
       </c>
       <c r="M17">
-        <v>7.28</v>
+        <v>7.98</v>
       </c>
       <c r="N17">
-        <v>7.29</v>
+        <v>7.99</v>
       </c>
       <c r="O17">
-        <v>7.64</v>
+        <v>8.64</v>
       </c>
       <c r="P17">
-        <v>7.68</v>
+        <v>8.68</v>
       </c>
       <c r="Q17">
-        <v>7.67</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1976,40 +1976,40 @@
         <v>8.23</v>
       </c>
       <c r="F18">
-        <v>7.6</v>
+        <v>9.2</v>
       </c>
       <c r="G18">
-        <v>7.58</v>
+        <v>9.58</v>
       </c>
       <c r="H18">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="I18">
         <v>5.98</v>
       </c>
       <c r="J18">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
       <c r="L18">
-        <v>7.64</v>
+        <v>8.3</v>
       </c>
       <c r="M18">
-        <v>7.81</v>
+        <v>8.3</v>
       </c>
       <c r="N18">
-        <v>7.64</v>
+        <v>8.34</v>
       </c>
       <c r="O18">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="P18">
-        <v>8.57</v>
+        <v>9.57</v>
       </c>
       <c r="Q18">
-        <v>8.33</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -2017,49 +2017,49 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="D19">
-        <v>8.01</v>
+        <v>8.61</v>
       </c>
       <c r="E19">
-        <v>8.22</v>
+        <v>8.72</v>
       </c>
       <c r="F19">
-        <v>8.79</v>
+        <v>9.29</v>
       </c>
       <c r="G19">
-        <v>8.66</v>
+        <v>9.26</v>
       </c>
       <c r="H19">
-        <v>8.69</v>
+        <v>9.39</v>
       </c>
       <c r="I19">
-        <v>4.58</v>
+        <v>6.49</v>
       </c>
       <c r="J19">
-        <v>4.28</v>
+        <v>6.38</v>
       </c>
       <c r="K19">
-        <v>4.32</v>
+        <v>6.52</v>
       </c>
       <c r="L19">
-        <v>7.84</v>
+        <v>8.15</v>
       </c>
       <c r="M19">
-        <v>7.72</v>
+        <v>8.12</v>
       </c>
       <c r="N19">
-        <v>7.65</v>
+        <v>8.15</v>
       </c>
       <c r="O19">
-        <v>8.79</v>
+        <v>9.79</v>
       </c>
       <c r="P19">
-        <v>9.05</v>
+        <v>9.55</v>
       </c>
       <c r="Q19">
-        <v>8.92</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -2067,13 +2067,13 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>7.91</v>
+        <v>8.52</v>
       </c>
       <c r="D20">
-        <v>8.07</v>
+        <v>8.7</v>
       </c>
       <c r="E20">
-        <v>8.07</v>
+        <v>8.7</v>
       </c>
       <c r="F20">
         <v>8.67</v>
@@ -2094,13 +2094,13 @@
         <v>5.78</v>
       </c>
       <c r="L20">
-        <v>7.74</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>7.72</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>7.72</v>
+        <v>8.02</v>
       </c>
       <c r="O20">
         <v>8.92</v>
@@ -2288,7 +2288,7 @@
         <v>5.98</v>
       </c>
       <c r="K25">
-        <v>6.04</v>
+        <v>6.24</v>
       </c>
       <c r="L25">
         <v>8.34</v>
@@ -2364,13 +2364,13 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>8.3</v>
+        <v>8.5</v>
       </c>
       <c r="D27">
         <v>8.43</v>
       </c>
       <c r="E27">
-        <v>8.28</v>
+        <v>8.38</v>
       </c>
       <c r="F27">
         <v>8.84</v>
@@ -2382,13 +2382,13 @@
         <v>8.7</v>
       </c>
       <c r="I27">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>6.32</v>
+        <v>6.02</v>
       </c>
       <c r="K27">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>8.06</v>
